--- a/LST_MST_Openstone_Infraworld.xlsx
+++ b/LST_MST_Openstone_Infraworld.xlsx
@@ -2424,7 +2424,7 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
